--- a/metrics/Metrics_Ablation_Study_RHm_DT_VPD.xlsx
+++ b/metrics/Metrics_Ablation_Study_RHm_DT_VPD.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.306135926878333</v>
+        <v>2.250299789172549</v>
       </c>
       <c r="C2" t="n">
-        <v>2.397534761189664</v>
+        <v>2.190823273497183</v>
       </c>
       <c r="D2" t="n">
-        <v>7.122639086074443</v>
+        <v>6.648149731820912</v>
       </c>
       <c r="E2" t="n">
-        <v>2.668827286670016</v>
+        <v>2.578400615075344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9106675819258834</v>
+        <v>0.9253298743179968</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9544463691431632</v>
+        <v>0.9622624284425616</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9555492728405184</v>
+        <v>0.9629469173796947</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8225338635916093</v>
+        <v>0.8419190205192265</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007796514241435237</v>
+        <v>2.553202795401594</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09840499035705763</v>
+        <v>2.616890303599437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4780263712961088</v>
+        <v>7.754357739724345</v>
       </c>
       <c r="M2" t="n">
-        <v>0.479425144830691</v>
+        <v>2.784664744583151</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4082591694585112</v>
+        <v>0.9166919902770952</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1010930799752634</v>
+        <v>0.9726153139461549</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1417641350700305</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9782721526678573</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8935936146258626</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.243078322165072</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.265235403622651</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.996865483911135</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.44884982877904</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.919044845815768</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9589581274776362</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9531608332887914</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8193111853473392</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.144450312730073</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.898154046942609</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6.633433314480026</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.575545246055682</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9210422404426394</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9662848867516682</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9657701034723993</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8505353507709221</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.0141822377432933</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.158428351561374</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.007132324380403343</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.007130411026381123</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.01422576186193097</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1445741373479807</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1765393064642338</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3537246104010279</v>
+        <v>0.3730919367410376</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2517565050846587</v>
+        <v>0.2405018254940803</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2478296523679032</v>
+        <v>0.27521800125423</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4978249214009913</v>
+        <v>0.5246122389481873</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9558015780742204</v>
+        <v>0.9560900993526096</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9798125742177139</v>
+        <v>0.9790884077510932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.984605269293098</v>
+        <v>0.9822120088062087</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8938632663310783</v>
+        <v>0.8882861256787912</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00602260558843204</v>
+        <v>0.2677210184891841</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03342857709145342</v>
+        <v>0.2219494129739057</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4900719734953722</v>
+        <v>0.1136469270284872</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4903466585023094</v>
+        <v>0.3371155989100582</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4409487515615983</v>
+        <v>0.9796136617401401</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02410212363013653</v>
+        <v>0.9948539597304009</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02151164890243427</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9925978762558851</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9395593675425576</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2350768298145621</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1765345110533802</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1133676291544248</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3367010976436294</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9616581922649352</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9865770900002816</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9854878846836166</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.9008791232275839</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.493533326012011</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.356616100758214</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4302787785857891</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6559563846672957</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.938157573335247</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9803700533865257</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9855992524798548</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.903769479598541</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.008473101152031093</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.04534879926276608</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.004153713658533342</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.005217529980906077</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01599957844547545</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0358159473781321</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.03126498234861488</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.12056564894753</v>
+        <v>1.10394300665744</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6696802929475248</v>
+        <v>0.6227074095899585</v>
       </c>
       <c r="D4" t="n">
-        <v>2.806280302351548</v>
+        <v>2.920074136749112</v>
       </c>
       <c r="E4" t="n">
-        <v>1.675195601221406</v>
+        <v>1.708822441551231</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9556864535923278</v>
+        <v>0.9586954384789618</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9777229868461338</v>
+        <v>0.9793007611978961</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9781251903493074</v>
+        <v>0.9766715722748759</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8797965255397691</v>
+        <v>0.8807651099842208</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006588665764361179</v>
+        <v>1.390030832311664</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1303102926814547</v>
+        <v>0.9321005630995591</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4903749248046813</v>
+        <v>3.323400658889203</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4866235557158323</v>
+        <v>1.82301965400519</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4331553251205861</v>
+        <v>0.9605310359209273</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08433496691356068</v>
+        <v>0.9882634786532726</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06965472459943806</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9872460379087358</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9291046014397268</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.22672856591558</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5760195471133684</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.062124084427378</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.015471181740731</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9004449696058304</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.955594394513319</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.952985131135927</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.840197165740927</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.9268485885138695</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5096893387134962</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.093843035864823</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.447011760790085</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9731870126332167</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9877079988308933</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.983669831071829</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9015936986343551</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01058742339627788</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1939872856863732</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.005493223393078506</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.006520523264676448</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01551946764713308</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1587814327316374</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.09776167054259594</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
